--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_los_lagos.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_los_lagos.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.96735438495421</v>
+      </c>
+      <c r="C2">
         <v>19.90422352644655</v>
-      </c>
-      <c r="C2">
-        <v>29.96735438495421</v>
       </c>
       <c r="D2">
         <v>5.024059334298118</v>
       </c>
       <c r="E2">
-        <v>13.28085271659266</v>
+        <v>19.99535522517148</v>
       </c>
       <c r="F2">
         <v>66.72379205823587</v>
       </c>
       <c r="G2">
-        <v>19.99535522517148</v>
+        <v>13.28085271659266</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.17592713644485</v>
+      </c>
+      <c r="C3">
         <v>28.99725454307753</v>
-      </c>
-      <c r="C3">
-        <v>29.17592713644485</v>
       </c>
       <c r="D3">
         <v>3.448602344454463</v>
       </c>
       <c r="E3">
-        <v>18.33259863345824</v>
+        <v>18.44555873925502</v>
       </c>
       <c r="F3">
         <v>63.22184262728675</v>
       </c>
       <c r="G3">
-        <v>18.44555873925502</v>
+        <v>18.33259863345824</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>29.99544833864361</v>
+      </c>
+      <c r="C4">
         <v>42.46700045516614</v>
-      </c>
-      <c r="C4">
-        <v>29.99544833864361</v>
       </c>
       <c r="D4">
         <v>2.354769560557342</v>
       </c>
       <c r="E4">
-        <v>24.62391132224862</v>
+        <v>17.39245183425706</v>
       </c>
       <c r="F4">
         <v>57.98363684349433</v>
       </c>
       <c r="G4">
-        <v>17.39245183425706</v>
+        <v>24.62391132224862</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.75590551181103</v>
+      </c>
+      <c r="C5">
         <v>35.5249343832021</v>
-      </c>
-      <c r="C5">
-        <v>27.75590551181103</v>
       </c>
       <c r="D5">
         <v>2.814924270410048</v>
       </c>
       <c r="E5">
-        <v>21.75695225847935</v>
+        <v>16.99887477897444</v>
       </c>
       <c r="F5">
         <v>61.24417296254622</v>
       </c>
       <c r="G5">
-        <v>16.99887477897444</v>
+        <v>21.75695225847935</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.45313371028112</v>
+      </c>
+      <c r="C6">
         <v>26.99689416261846</v>
-      </c>
-      <c r="C6">
-        <v>30.45313371028112</v>
       </c>
       <c r="D6">
         <v>3.704129793510325</v>
       </c>
       <c r="E6">
+        <v>19.34145971372211</v>
+      </c>
+      <c r="F6">
+        <v>63.5122148601487</v>
+      </c>
+      <c r="G6">
         <v>17.14632542612918</v>
-      </c>
-      <c r="F6">
-        <v>63.51221486014871</v>
-      </c>
-      <c r="G6">
-        <v>19.34145971372212</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.54609529179588</v>
+      </c>
+      <c r="C7">
         <v>35.18466309557373</v>
-      </c>
-      <c r="C7">
-        <v>29.54609529179588</v>
       </c>
       <c r="D7">
         <v>2.842147435897436</v>
       </c>
       <c r="E7">
-        <v>21.35889098066061</v>
+        <v>17.93599178504193</v>
       </c>
       <c r="F7">
         <v>60.70511723429744</v>
       </c>
       <c r="G7">
-        <v>17.93599178504193</v>
+        <v>21.35889098066061</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.70761670761671</v>
+      </c>
+      <c r="C8">
         <v>27.11711711711712</v>
-      </c>
-      <c r="C8">
-        <v>26.70761670761671</v>
       </c>
       <c r="D8">
         <v>3.687707641196013</v>
       </c>
       <c r="E8">
+        <v>17.36236822489618</v>
+      </c>
+      <c r="F8">
+        <v>65.00905121925248</v>
+      </c>
+      <c r="G8">
         <v>17.62858055585135</v>
-      </c>
-      <c r="F8">
-        <v>65.00905121925247</v>
-      </c>
-      <c r="G8">
-        <v>17.36236822489618</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>25.85547290116897</v>
+      </c>
+      <c r="C9">
         <v>36.89691817215728</v>
-      </c>
-      <c r="C9">
-        <v>25.85547290116897</v>
       </c>
       <c r="D9">
         <v>2.710253456221198</v>
       </c>
       <c r="E9">
+        <v>15.88638589618022</v>
+      </c>
+      <c r="F9">
+        <v>61.4430297094352</v>
+      </c>
+      <c r="G9">
         <v>22.67058439438459</v>
-      </c>
-      <c r="F9">
-        <v>61.44302970943519</v>
-      </c>
-      <c r="G9">
-        <v>15.88638589618021</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.80968702083521</v>
+      </c>
+      <c r="C10">
         <v>22.39559844863354</v>
-      </c>
-      <c r="C10">
-        <v>29.80968702083521</v>
       </c>
       <c r="D10">
         <v>4.465163109142167</v>
       </c>
       <c r="E10">
-        <v>14.71407407407407</v>
+        <v>19.58518518518519</v>
       </c>
       <c r="F10">
         <v>65.70074074074074</v>
       </c>
       <c r="G10">
-        <v>19.58518518518519</v>
+        <v>14.71407407407407</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.38073028898663</v>
+      </c>
+      <c r="C11">
         <v>22.2865070696933</v>
-      </c>
-      <c r="C11">
-        <v>26.38073028898663</v>
       </c>
       <c r="D11">
         <v>4.487019867549669</v>
       </c>
       <c r="E11">
-        <v>14.99086649193868</v>
+        <v>17.74481772694782</v>
       </c>
       <c r="F11">
         <v>67.2643157811135</v>
       </c>
       <c r="G11">
-        <v>17.74481772694782</v>
+        <v>14.99086649193868</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>26.17755513810617</v>
+      </c>
+      <c r="C12">
         <v>29.70848117999026</v>
-      </c>
-      <c r="C12">
-        <v>26.17755513810617</v>
       </c>
       <c r="D12">
         <v>3.366042154566745</v>
       </c>
       <c r="E12">
-        <v>19.05782062440026</v>
+        <v>16.79275177969695</v>
       </c>
       <c r="F12">
         <v>64.14942759590279</v>
       </c>
       <c r="G12">
-        <v>16.79275177969695</v>
+        <v>19.05782062440026</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>27.59049891090136</v>
+      </c>
+      <c r="C13">
         <v>26.90592262213463</v>
-      </c>
-      <c r="C13">
-        <v>27.59049891090136</v>
       </c>
       <c r="D13">
         <v>3.716653816499615</v>
       </c>
       <c r="E13">
-        <v>17.41524001342733</v>
+        <v>17.85834172541121</v>
       </c>
       <c r="F13">
-        <v>64.72641826116147</v>
+        <v>64.72641826116146</v>
       </c>
       <c r="G13">
-        <v>17.85834172541121</v>
+        <v>17.41524001342732</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>29.48381452318461</v>
+      </c>
+      <c r="C14">
         <v>34.7769028871391</v>
-      </c>
-      <c r="C14">
-        <v>29.48381452318461</v>
       </c>
       <c r="D14">
         <v>2.875471698113207</v>
       </c>
       <c r="E14">
-        <v>21.17177097203728</v>
+        <v>17.94940079893476</v>
       </c>
       <c r="F14">
         <v>60.87882822902797</v>
       </c>
       <c r="G14">
-        <v>17.94940079893476</v>
+        <v>21.17177097203728</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>30.12273767422509</v>
+      </c>
+      <c r="C15">
         <v>24.36030788433535</v>
-      </c>
-      <c r="C15">
-        <v>30.12273767422509</v>
       </c>
       <c r="D15">
         <v>4.105038428693424</v>
       </c>
       <c r="E15">
-        <v>15.76892001077296</v>
+        <v>19.49905736601131</v>
       </c>
       <c r="F15">
         <v>64.73202262321573</v>
       </c>
       <c r="G15">
-        <v>19.49905736601131</v>
+        <v>15.76892001077296</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>24.73251028806584</v>
+      </c>
+      <c r="C16">
         <v>36.66666666666666</v>
-      </c>
-      <c r="C16">
-        <v>24.73251028806584</v>
       </c>
       <c r="D16">
         <v>2.727272727272727</v>
       </c>
       <c r="E16">
-        <v>22.71800101988782</v>
+        <v>15.32381438041815</v>
       </c>
       <c r="F16">
         <v>61.95818459969404</v>
       </c>
       <c r="G16">
-        <v>15.32381438041815</v>
+        <v>22.71800101988782</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.72079772079772</v>
+      </c>
+      <c r="C17">
         <v>30.1994301994302</v>
-      </c>
-      <c r="C17">
-        <v>27.72079772079772</v>
       </c>
       <c r="D17">
         <v>3.311320754716981</v>
       </c>
       <c r="E17">
-        <v>19.12321847375068</v>
+        <v>17.55367129713152</v>
       </c>
       <c r="F17">
         <v>63.32311022911781</v>
       </c>
       <c r="G17">
-        <v>17.55367129713152</v>
+        <v>19.12321847375068</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>31.04454284970044</v>
+      </c>
+      <c r="C18">
         <v>17.69731700963793</v>
-      </c>
-      <c r="C18">
-        <v>31.04454284970044</v>
       </c>
       <c r="D18">
         <v>5.650574035914042</v>
       </c>
       <c r="E18">
-        <v>11.89800707505867</v>
+        <v>20.87142306749326</v>
       </c>
       <c r="F18">
         <v>67.23056985744807</v>
       </c>
       <c r="G18">
-        <v>20.87142306749326</v>
+        <v>11.89800707505867</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>27.98693814829043</v>
+      </c>
+      <c r="C19">
         <v>34.40261237034191</v>
-      </c>
-      <c r="C19">
-        <v>27.98693814829043</v>
       </c>
       <c r="D19">
         <v>2.906756002233389</v>
       </c>
       <c r="E19">
-        <v>21.18523775727466</v>
+        <v>17.23444523302578</v>
       </c>
       <c r="F19">
         <v>61.58031700969955</v>
       </c>
       <c r="G19">
-        <v>17.23444523302578</v>
+        <v>21.18523775727466</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>26.80876026593664</v>
+      </c>
+      <c r="C20">
         <v>33.8482596793117</v>
-      </c>
-      <c r="C20">
-        <v>26.80876026593664</v>
       </c>
       <c r="D20">
         <v>2.954361640670133</v>
       </c>
       <c r="E20">
-        <v>21.06864654333009</v>
+        <v>16.68695228821811</v>
       </c>
       <c r="F20">
         <v>62.24440116845179</v>
       </c>
       <c r="G20">
-        <v>16.68695228821811</v>
+        <v>21.06864654333009</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>27.94080052589292</v>
+      </c>
+      <c r="C21">
         <v>27.26517420203053</v>
-      </c>
-      <c r="C21">
-        <v>27.94080052589292</v>
       </c>
       <c r="D21">
         <v>3.667682416368081</v>
       </c>
       <c r="E21">
+        <v>18.00240008470887</v>
+      </c>
+      <c r="F21">
+        <v>64.43050931209336</v>
+      </c>
+      <c r="G21">
         <v>17.56709060319776</v>
-      </c>
-      <c r="F21">
-        <v>64.43050931209338</v>
-      </c>
-      <c r="G21">
-        <v>18.00240008470887</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>30.19738055709279</v>
+      </c>
+      <c r="C22">
         <v>31.72846338313964</v>
-      </c>
-      <c r="C22">
-        <v>30.19738055709279</v>
       </c>
       <c r="D22">
         <v>3.151744186046511</v>
       </c>
       <c r="E22">
-        <v>19.59444064707222</v>
+        <v>18.64889496468444</v>
       </c>
       <c r="F22">
         <v>61.75666438824333</v>
       </c>
       <c r="G22">
-        <v>18.64889496468444</v>
+        <v>19.59444064707222</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>28.65414710485133</v>
+      </c>
+      <c r="C23">
         <v>35.72769953051643</v>
-      </c>
-      <c r="C23">
-        <v>28.65414710485133</v>
       </c>
       <c r="D23">
         <v>2.798948751642576</v>
       </c>
       <c r="E23">
-        <v>21.73457730388424</v>
+        <v>17.43145468392993</v>
       </c>
       <c r="F23">
         <v>60.83396801218584</v>
       </c>
       <c r="G23">
-        <v>17.43145468392994</v>
+        <v>21.73457730388424</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>24.83041085370536</v>
+      </c>
+      <c r="C24">
         <v>32.43312428004608</v>
-      </c>
-      <c r="C24">
-        <v>24.83041085370536</v>
       </c>
       <c r="D24">
         <v>3.083267561168114</v>
       </c>
       <c r="E24">
-        <v>20.62342313013755</v>
+        <v>15.78904533246521</v>
       </c>
       <c r="F24">
         <v>63.58753153739725</v>
       </c>
       <c r="G24">
-        <v>15.78904533246521</v>
+        <v>20.62342313013755</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.78936605316973</v>
+      </c>
+      <c r="C25">
         <v>34.75460122699386</v>
-      </c>
-      <c r="C25">
-        <v>26.78936605316973</v>
       </c>
       <c r="D25">
         <v>2.877316857899382</v>
       </c>
       <c r="E25">
-        <v>21.51401987467561</v>
+        <v>16.58332805873789</v>
       </c>
       <c r="F25">
         <v>61.90265206658649</v>
       </c>
       <c r="G25">
-        <v>16.58332805873789</v>
+        <v>21.51401987467561</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.47603833865815</v>
+      </c>
+      <c r="C26">
         <v>43.88407120036513</v>
-      </c>
-      <c r="C26">
-        <v>27.47603833865815</v>
       </c>
       <c r="D26">
         <v>2.27873114924597</v>
       </c>
       <c r="E26">
-        <v>25.60926887734718</v>
+        <v>16.03409242242642</v>
       </c>
       <c r="F26">
         <v>58.35663870022639</v>
       </c>
       <c r="G26">
-        <v>16.03409242242642</v>
+        <v>25.60926887734718</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>22.21926910299003</v>
+      </c>
+      <c r="C27">
         <v>36.33222591362127</v>
-      </c>
-      <c r="C27">
-        <v>22.21926910299003</v>
       </c>
       <c r="D27">
         <v>2.752377468910022</v>
       </c>
       <c r="E27">
-        <v>22.91509513033274</v>
+        <v>14.01391333500964</v>
       </c>
       <c r="F27">
         <v>63.07099153465761</v>
       </c>
       <c r="G27">
-        <v>14.01391333500964</v>
+        <v>22.91509513033274</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>25.93811718235681</v>
+      </c>
+      <c r="C28">
         <v>28.60434496379197</v>
-      </c>
-      <c r="C28">
-        <v>25.93811718235681</v>
       </c>
       <c r="D28">
         <v>3.495972382048331</v>
       </c>
       <c r="E28">
-        <v>18.50905218317359</v>
+        <v>16.78381256656017</v>
       </c>
       <c r="F28">
         <v>64.70713525026625</v>
       </c>
       <c r="G28">
-        <v>16.78381256656017</v>
+        <v>18.50905218317359</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>39.66666666666666</v>
+      </c>
+      <c r="C29">
         <v>31.86666666666667</v>
-      </c>
-      <c r="C29">
-        <v>39.66666666666666</v>
       </c>
       <c r="D29">
         <v>3.138075313807531</v>
       </c>
       <c r="E29">
-        <v>18.57753595025262</v>
+        <v>23.12475709288768</v>
       </c>
       <c r="F29">
         <v>58.2977069568597</v>
       </c>
       <c r="G29">
-        <v>23.12475709288768</v>
+        <v>18.57753595025262</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>30.89666951323655</v>
+      </c>
+      <c r="C30">
         <v>25.3800170794193</v>
-      </c>
-      <c r="C30">
-        <v>30.89666951323655</v>
       </c>
       <c r="D30">
         <v>3.940107671601615</v>
       </c>
       <c r="E30">
-        <v>16.24043715846994</v>
+        <v>19.77049180327869</v>
       </c>
       <c r="F30">
         <v>63.98907103825136</v>
       </c>
       <c r="G30">
-        <v>19.77049180327869</v>
+        <v>16.24043715846994</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>28.90625</v>
+      </c>
+      <c r="C31">
         <v>35.078125</v>
-      </c>
-      <c r="C31">
-        <v>28.90625</v>
       </c>
       <c r="D31">
         <v>2.850779510022272</v>
       </c>
       <c r="E31">
-        <v>21.3911386374464</v>
+        <v>17.62744163887566</v>
       </c>
       <c r="F31">
         <v>60.98141972367794</v>
       </c>
       <c r="G31">
-        <v>17.62744163887566</v>
+        <v>21.3911386374464</v>
       </c>
     </row>
   </sheetData>
